--- a/gcam-data-system/energy-data/assumptions/Tables_A20s_R.xlsx
+++ b/gcam-data-system/energy-data/assumptions/Tables_A20s_R.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="23416"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="0" windowWidth="15660" windowHeight="12240" tabRatio="500"/>
+    <workbookView xWindow="240" yWindow="0" windowWidth="15660" windowHeight="12240" tabRatio="500" firstSheet="2" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="A21.unoil_demandshares.csv" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="28">
   <si>
     <t>nuclear</t>
   </si>
@@ -75,9 +75,6 @@
   </si>
   <si>
     <t>supplysector</t>
-  </si>
-  <si>
-    <t>region</t>
   </si>
   <si>
     <t># Renewables tuned by region to match near term trends (see proposal 91).</t>
@@ -568,20 +565,20 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -724,17 +721,17 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
@@ -754,7 +751,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D4">
         <v>0.06</v>
@@ -768,7 +765,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5">
         <v>0.26</v>
@@ -782,7 +779,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6">
         <v>0.26</v>
@@ -796,7 +793,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>0.06</v>
@@ -810,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8">
         <v>0.12</v>
@@ -824,7 +821,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D9">
         <v>0.01</v>
@@ -838,7 +835,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10">
         <v>0.15</v>
@@ -852,7 +849,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D11">
         <v>0.25</v>
@@ -866,7 +863,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12">
         <v>0.06</v>
@@ -880,7 +877,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D13">
         <v>0.06</v>
@@ -894,7 +891,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D14">
         <v>0.02</v>
@@ -908,7 +905,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D15">
         <v>0.06</v>
@@ -922,7 +919,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>0.3</v>
@@ -936,7 +933,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D17">
         <v>1.9</v>
@@ -950,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D18">
         <v>0.1</v>
@@ -964,7 +961,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D19">
         <v>0.1</v>
@@ -978,7 +975,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D20">
         <v>0.1</v>
@@ -992,7 +989,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D21">
         <v>0.1</v>
@@ -1006,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D22">
         <v>0.1</v>
@@ -1020,7 +1017,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D23">
         <v>0.1</v>
@@ -1034,7 +1031,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D24">
         <v>0.1</v>
@@ -1048,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D25">
         <v>0.1</v>
@@ -1062,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D26">
         <v>0.1</v>
@@ -1076,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D27">
         <v>0.1</v>
@@ -1090,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D28">
         <v>0.1</v>
@@ -1104,7 +1101,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D29">
         <v>0.1</v>
@@ -1118,7 +1115,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30">
         <v>0.1</v>
@@ -1132,7 +1129,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D31">
         <v>0.1</v>
@@ -1146,7 +1143,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D32">
         <v>0.17</v>
@@ -1160,7 +1157,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D33">
         <v>0.2</v>
@@ -1174,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D34">
         <v>0.33</v>
@@ -1188,7 +1185,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D35">
         <v>0.05</v>
@@ -1202,7 +1199,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D36">
         <v>0.33</v>
@@ -1216,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D37">
         <v>0.04</v>
@@ -1230,7 +1227,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D38">
         <v>0.1</v>
@@ -1244,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D39">
         <v>0.33</v>
@@ -1258,7 +1255,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D40">
         <v>0.06</v>
@@ -1272,7 +1269,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D41">
         <v>0.3</v>
@@ -1286,7 +1283,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D42">
         <v>0.04</v>
@@ -1300,7 +1297,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D43">
         <v>0.33</v>
@@ -1314,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D44">
         <v>0.33</v>
@@ -1328,7 +1325,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D45">
         <v>0.36</v>
@@ -1342,7 +1339,7 @@
         <v>1</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D46">
         <v>0.02</v>
@@ -1356,7 +1353,7 @@
         <v>1</v>
       </c>
       <c r="C47" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D47">
         <v>0.15</v>
@@ -1370,7 +1367,7 @@
         <v>1</v>
       </c>
       <c r="C48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D48">
         <v>0.15</v>
@@ -1384,7 +1381,7 @@
         <v>1</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D49">
         <v>0.15</v>
@@ -1398,7 +1395,7 @@
         <v>1</v>
       </c>
       <c r="C50" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D50">
         <v>0.15</v>
@@ -1412,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D51">
         <v>0.01</v>
@@ -1426,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="C52" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D52">
         <v>0.15</v>
@@ -1440,7 +1437,7 @@
         <v>1</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D53">
         <v>0.15</v>
@@ -1454,7 +1451,7 @@
         <v>1</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D54">
         <v>0.15</v>
@@ -1468,7 +1465,7 @@
         <v>1</v>
       </c>
       <c r="C55" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D55">
         <v>0.03</v>
@@ -1482,7 +1479,7 @@
         <v>1</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D56">
         <v>0.03</v>
@@ -1496,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C57" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D57">
         <v>0.15</v>
@@ -1510,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D58">
         <v>0.15</v>
@@ -1541,17 +1538,17 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B3" t="s">
         <v>17</v>
